--- a/test_data/UltraArm_P1_Attachments.xlsx
+++ b/test_data/UltraArm_P1_Attachments.xlsx
@@ -3,19 +3,22 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22188" windowHeight="10500" tabRatio="600" firstSheet="1" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="5" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="open_laser" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="get_gripper_angle" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="set_gripper_angle" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="set_gripper_zero" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="get_gripper_run_status" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="get_gripper_parameter" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="set_gripper_enable_status" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="set_pump_state" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="close_laser" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="set_gripper_parameter" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="get_gripper_angle" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="set_gripper_angle" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="set_gripper_zero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="get_gripper_run_status" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="get_gripper_parameter" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="set_gripper_enable_status" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="set_pump_state" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="set_gripper_parameter" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="quick_off_laser" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="set_pwm_laser" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="quick_off_custom_pwm" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="set_pwm_custom" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="get_pwm_status" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1016,15 +1019,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <cols>
-    <col width="13.2222222222222" customWidth="1" style="2" min="1" max="1"/>
-    <col width="20.8796296296296" customWidth="1" style="1" min="2" max="2"/>
+    <col width="13.2181818181818" customWidth="1" style="2" min="1" max="1"/>
+    <col width="20.8818181818182" customWidth="1" style="1" min="2" max="2"/>
     <col width="18" customWidth="1" style="1" min="3" max="3"/>
     <col width="9" customWidth="1" style="1" min="4" max="4"/>
-    <col width="22.6296296296296" customWidth="1" style="1" min="5" max="5"/>
-    <col width="13.5555555555556" customWidth="1" style="1" min="6" max="6"/>
+    <col width="22.6272727272727" customWidth="1" style="1" min="5" max="5"/>
+    <col width="13.5545454545455" customWidth="1" style="1" min="6" max="6"/>
     <col width="9" customWidth="1" style="1" min="7" max="16384"/>
   </cols>
   <sheetData>
@@ -1066,18 +1069,99 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>打开激光</t>
+          <t>读取夹爪角度</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>open_laser</t>
-        </is>
+          <t>get_gripper_angle</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>30</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>读取夹爪角度</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>get_gripper_angle</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>读取夹爪角度</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>get_gripper_angle</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>90</v>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>读取夹爪角度</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>get_gripper_angle</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
@@ -1095,7 +1179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,20 +1200,15 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>p_value</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>expect_data</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
-        <is>
-          <t>expect_data</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
         <is>
           <t>test_type</t>
         </is>
@@ -1141,24 +1220,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>设置夹爪参数</t>
+          <t>设置激光PWM最小档位</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>set_gripper_parameter</t>
+          <t>set_pwm_laser</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
@@ -1170,23 +1248,364 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>地址越界</t>
+          <t>设置激光PWM最大档位</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>set_gripper_parameter</t>
+          <t>set_pwm_laser</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>255</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>激光PWM档位越界</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>set_pwm_laser</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>256</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>expect_data</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>test_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>打开自定义PWM模式</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>quick_off_custom_pwm</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>关闭自定义PWM模式</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>quick_off_custom_pwm</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>normal_off</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>自定义PWM模式状态越界</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>quick_off_custom_pwm</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>exception</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>expect_data</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>test_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>设置自定义PWM最小档位</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>set_pwm_custom</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>设置自定义PWM最大档位</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>set_pwm_custom</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>255</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>自定义PWM档位越界</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>set_pwm_custom</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>256</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>expect_data</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>test_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>读取PWM默认关闭状态</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>get_pwm_status</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>[0,0,0,0]</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -1201,19 +1620,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="4"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="13.2222222222222" customWidth="1" style="2" min="1" max="1"/>
-    <col width="20.8796296296296" customWidth="1" style="1" min="2" max="2"/>
+    <col width="13.2181818181818" customWidth="1" style="2" min="1" max="1"/>
+    <col width="20.8818181818182" customWidth="1" style="1" min="2" max="2"/>
     <col width="18" customWidth="1" style="1" min="3" max="3"/>
     <col width="9" customWidth="1" style="1" min="4" max="4"/>
-    <col width="22.6296296296296" customWidth="1" style="1" min="5" max="5"/>
-    <col width="13.5555555555556" customWidth="1" style="1" min="6" max="6"/>
-    <col width="9" customWidth="1" style="1" min="7" max="16384"/>
+    <col width="22.6272727272727" customWidth="1" style="1" min="5" max="6"/>
+    <col width="13.5545454545455" customWidth="1" style="1" min="7" max="7"/>
+    <col width="9" customWidth="1" style="1" min="8" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" customFormat="1" customHeight="1" s="1">
+    <row r="1" customFormat="1" s="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>ID</t>
@@ -1231,15 +1650,20 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>speed</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>expect_data</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>test_type</t>
         </is>
@@ -1251,101 +1675,217 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>读取夹爪角度</t>
+          <t>设置夹爪角度</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>get_gripper_angle</t>
+          <t>set_gripper_angle</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
         <v>30</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
+        <v>100</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" customFormat="1" s="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>读取夹爪角度</t>
+          <t>设置夹爪角度</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>get_gripper_angle</t>
+          <t>set_gripper_angle</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
         <v>60</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
+        <v>50</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" customFormat="1" s="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>读取夹爪角度</t>
+          <t>设置夹爪角度</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>get_gripper_angle</t>
+          <t>set_gripper_angle</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
         <v>90</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
+        <v>60</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" customFormat="1" s="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>读取夹爪角度</t>
+          <t>设置夹爪角度</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>get_gripper_angle</t>
+          <t>set_gripper_angle</t>
         </is>
       </c>
       <c r="D5" s="1" t="n">
         <v>100</v>
       </c>
       <c r="E5" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28.8" customHeight="1" s="3">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>设置夹爪角度（角度超限）</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>set_gripper_angle</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28.8" customHeight="1" s="3">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>设置夹爪角度（角度超限）</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>set_gripper_angle</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28.8" customHeight="1" s="3">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>设置夹爪角度（速度超限）</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>set_gripper_angle</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
+      <c r="E8" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t>exception</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="28.8" customHeight="1" s="3">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>设置夹爪角度（速度超限）</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>set_gripper_angle</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>exception</t>
         </is>
       </c>
     </row>
@@ -1361,19 +1901,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1"/>
   <cols>
-    <col width="13.2222222222222" customWidth="1" style="2" min="1" max="1"/>
-    <col width="20.8796296296296" customWidth="1" style="1" min="2" max="2"/>
+    <col width="13.2181818181818" customWidth="1" style="2" min="1" max="1"/>
+    <col width="20.8818181818182" customWidth="1" style="1" min="2" max="2"/>
     <col width="18" customWidth="1" style="1" min="3" max="3"/>
     <col width="9" customWidth="1" style="1" min="4" max="4"/>
-    <col width="22.6296296296296" customWidth="1" style="1" min="5" max="6"/>
-    <col width="13.5555555555556" customWidth="1" style="1" min="7" max="7"/>
-    <col width="9" customWidth="1" style="1" min="8" max="16384"/>
+    <col width="22.6272727272727" customWidth="1" style="1" min="5" max="5"/>
+    <col width="13.5545454545455" customWidth="1" style="1" min="6" max="6"/>
+    <col width="9" customWidth="1" style="1" min="7" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" s="1">
+    <row r="1" ht="28.8" customFormat="1" customHeight="1" s="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>ID</t>
@@ -1391,20 +1931,15 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>speed</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
           <t>expect_data</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>test_type</t>
         </is>
@@ -1416,223 +1951,25 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>设置夹爪角度</t>
+          <t>设置夹爪零位</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>set_gripper_angle</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>30</v>
+          <t>set_gripper_zero</t>
+        </is>
       </c>
       <c r="E2" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="F2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
-    <row r="3" customFormat="1" s="1">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>设置夹爪角度</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>set_gripper_angle</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" customFormat="1" s="1">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>设置夹爪角度</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>set_gripper_angle</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" customFormat="1" s="1">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>设置夹爪角度</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>set_gripper_angle</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="28.8" customHeight="1" s="3">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>设置夹爪角度（角度超限）</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>set_gripper_angle</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>101</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="28.8" customHeight="1" s="3">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>设置夹爪角度（角度超限）</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>set_gripper_angle</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28.8" customHeight="1" s="3">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>设置夹爪角度（速度超限）</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>set_gripper_angle</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>101</v>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>exception</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="28.8" customHeight="1" s="3">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>设置夹爪角度（速度超限）</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>set_gripper_angle</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>exception</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1642,15 +1979,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2"/>
   <cols>
-    <col width="13.2222222222222" customWidth="1" style="2" min="1" max="1"/>
-    <col width="20.8796296296296" customWidth="1" style="1" min="2" max="2"/>
+    <col width="13.2181818181818" customWidth="1" style="2" min="1" max="1"/>
+    <col width="20.8818181818182" customWidth="1" style="1" min="2" max="2"/>
     <col width="18" customWidth="1" style="1" min="3" max="3"/>
     <col width="9" customWidth="1" style="1" min="4" max="4"/>
-    <col width="22.6296296296296" customWidth="1" style="1" min="5" max="5"/>
-    <col width="13.5555555555556" customWidth="1" style="1" min="6" max="6"/>
+    <col width="22.6272727272727" customWidth="1" style="1" min="5" max="5"/>
+    <col width="13.5545454545455" customWidth="1" style="1" min="6" max="6"/>
     <col width="9" customWidth="1" style="1" min="7" max="16384"/>
   </cols>
   <sheetData>
@@ -1692,12 +2029,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>设置夹爪零位</t>
+          <t>获取夹爪静止时运动状态</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>set_gripper_zero</t>
+          <t>get_gripper_run_status</t>
         </is>
       </c>
       <c r="E2" s="1" t="n">
@@ -1706,6 +2043,29 @@
       <c r="F2" s="1" t="inlineStr">
         <is>
           <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28.8" customHeight="1" s="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>获取夹爪运动时运动状态</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>get_gripper_run_status</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>normal1</t>
         </is>
       </c>
     </row>
@@ -1720,16 +2080,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2"/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
   <cols>
-    <col width="13.2222222222222" customWidth="1" style="2" min="1" max="1"/>
-    <col width="20.8796296296296" customWidth="1" style="1" min="2" max="2"/>
+    <col width="13.2181818181818" customWidth="1" style="2" min="1" max="1"/>
+    <col width="20.8818181818182" customWidth="1" style="1" min="2" max="2"/>
     <col width="18" customWidth="1" style="1" min="3" max="3"/>
     <col width="9" customWidth="1" style="1" min="4" max="4"/>
-    <col width="22.6296296296296" customWidth="1" style="1" min="5" max="5"/>
-    <col width="13.5555555555556" customWidth="1" style="1" min="6" max="6"/>
-    <col width="9" customWidth="1" style="1" min="7" max="16384"/>
+    <col width="22.6272727272727" customWidth="1" style="1" min="5" max="6"/>
+    <col width="13.5545454545455" customWidth="1" style="1" min="7" max="7"/>
+    <col width="9" customWidth="1" style="1" min="8" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.8" customFormat="1" customHeight="1" s="1">
@@ -1755,10 +2115,15 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
           <t>expect_data</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>test_type</t>
         </is>
@@ -1770,43 +2135,84 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>获取夹爪静止时运动状态</t>
+          <t>获取夹爪参数</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>get_gripper_run_status</t>
-        </is>
+          <t>get_gripper_parameter</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>21</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="28.8" customHeight="1" s="3">
+    <row r="3" ht="28.8" customFormat="1" customHeight="1" s="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>获取夹爪运动时运动状态</t>
+          <t>获取夹爪参数</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>get_gripper_run_status</t>
-        </is>
+          <t>get_gripper_parameter</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>22</v>
       </c>
       <c r="E3" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28.8" customHeight="1" s="3">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>获取夹爪参数</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>get_gripper_parameter</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>normal1</t>
+      <c r="F4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>normal</t>
         </is>
       </c>
     </row>
@@ -1821,19 +2227,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
   <cols>
-    <col width="13.2222222222222" customWidth="1" style="2" min="1" max="1"/>
-    <col width="20.8796296296296" customWidth="1" style="1" min="2" max="2"/>
+    <col width="13.2181818181818" customWidth="1" style="2" min="1" max="1"/>
+    <col width="20.8818181818182" customWidth="1" style="1" min="2" max="2"/>
     <col width="18" customWidth="1" style="1" min="3" max="3"/>
     <col width="9" customWidth="1" style="1" min="4" max="4"/>
-    <col width="22.6296296296296" customWidth="1" style="1" min="5" max="6"/>
-    <col width="13.5555555555556" customWidth="1" style="1" min="7" max="7"/>
-    <col width="9" customWidth="1" style="1" min="8" max="16384"/>
+    <col width="22.6272727272727" customWidth="1" style="1" min="5" max="5"/>
+    <col width="13.5545454545455" customWidth="1" style="1" min="6" max="6"/>
+    <col width="9" customWidth="1" style="1" min="7" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" customFormat="1" customHeight="1" s="1">
+    <row r="1" customFormat="1" s="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
           <t>ID</t>
@@ -1851,20 +2257,15 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
           <t>expect_data</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>test_type</t>
         </is>
@@ -1876,21 +2277,23 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>获取夹爪参数</t>
+          <t>设置夹爪掉使能</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>get_gripper_parameter</t>
+          <t>set_gripper_enable_status</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="F2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
@@ -1902,49 +2305,48 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>获取夹爪参数</t>
+          <t>设置夹爪上使能</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>get_gripper_parameter</t>
+          <t>set_gripper_enable_status</t>
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="F3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="28.8" customHeight="1" s="3">
+    <row r="4" ht="28" customHeight="1" s="3">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>获取夹爪参数</t>
+          <t>设置使能状态超限</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>get_gripper_parameter</t>
+          <t>set_gripper_enable_status</t>
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
+        <v>2</v>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>exception</t>
         </is>
       </c>
     </row>
@@ -1959,99 +2361,145 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2"/>
-  <cols>
-    <col width="13.2222222222222" customWidth="1" style="2" min="1" max="1"/>
-    <col width="20.8796296296296" customWidth="1" style="1" min="2" max="2"/>
-    <col width="18" customWidth="1" style="1" min="3" max="3"/>
-    <col width="9" customWidth="1" style="1" min="4" max="4"/>
-    <col width="22.6296296296296" customWidth="1" style="1" min="5" max="5"/>
-    <col width="13.5555555555556" customWidth="1" style="1" min="6" max="6"/>
-    <col width="9" customWidth="1" style="1" min="7" max="16384"/>
-  </cols>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
   <sheetData>
-    <row r="1" customFormat="1" s="1">
-      <c r="A1" s="2" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>pump_state</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>expect_data</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>test_type</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="1">
-      <c r="A2" s="2" t="n">
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>设置夹爪掉使能</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>set_gripper_enable_status</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="n">
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>打开吸泵</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>set_pump_state</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>释放吸泵</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>set_pump_state</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28.8" customFormat="1" customHeight="1" s="1">
-      <c r="A3" s="2" t="n">
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>normal_release</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>关闭吸泵</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>set_pump_state</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>设置夹爪上使能</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>set_gripper_enable_status</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>normal</t>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>normal_close</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>状态越界</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>set_pump_state</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>exception</t>
         </is>
       </c>
     </row>
@@ -2066,8 +2514,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2"/>
+  <cols>
+    <col width="19.4545454545455" customWidth="1" style="3" min="2" max="2"/>
+    <col width="16.5454545454545" customWidth="1" style="3" min="3" max="3"/>
+    <col width="18.8181818181818" customWidth="1" style="3" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
@@ -2087,15 +2540,20 @@
       </c>
       <c r="D1" s="0" t="inlineStr">
         <is>
-          <t>pump_state</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="E1" s="0" t="inlineStr">
         <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
           <t>expect_data</t>
         </is>
       </c>
-      <c r="F1" s="0" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>test_type</t>
         </is>
@@ -2107,23 +2565,26 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>打开吸泵</t>
+          <t>设置夹爪参数</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>set_pump_state</t>
+          <t>set_gripper_parameter</t>
         </is>
       </c>
       <c r="D2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
+        <v>21</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="F2" s="0" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
@@ -2135,74 +2596,21 @@
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>释放吸泵</t>
+          <t>地址越界</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>set_pump_state</t>
+          <t>set_gripper_parameter</t>
         </is>
       </c>
       <c r="D3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="0" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F3" s="0" t="inlineStr">
-        <is>
-          <t>normal_release</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>关闭吸泵</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>set_pump_state</t>
-        </is>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F4" s="0" t="inlineStr">
-        <is>
-          <t>normal_close</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>状态越界</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>set_pump_state</t>
-        </is>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="0" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>exception</t>
         </is>
@@ -2219,7 +2627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2260,25 +2668,76 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>关闭激光</t>
+          <t>打开激光PWM模式</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>set_pwm_laser_mode</t>
+          <t>quick_off_laser</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>关闭激光PWM模式</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>quick_off_laser</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>normal</t>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>normal_off</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>激光模式状态越界</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>quick_off_laser</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>exception</t>
         </is>
       </c>
     </row>
